--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -23,13 +23,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFallergySeverity</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFallergySeverity</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:56:35+00:00</t>
+    <t>2023-11-09T22:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +80,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet VF_allergySeverity</t>
+    <t>Use the link in the Expansion section to navigate to the ConceptMap.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +80,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Use the link in the Expansion section to navigate to the ConceptMap.</t>
+    <t>Navigate to the [ConceptMap VF_allergySeverity](ConceptMap-CMVFallergySeverity.html).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
+    <sheet name="Include from 120.85-14.5" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -35,28 +36,28 @@
     <t>Name</t>
   </si>
   <si>
+    <t>VSVFallergySeverity</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
     <t>VF_allergySeverity</t>
   </si>
   <si>
-    <t>Title</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Navigate to the [ConceptMap VF_allergySeverity](ConceptMap-CMVFallergySeverity.html).</t>
+    <t>Navigate to [ConceptMap VF_allergySeverity](ConceptMap-CMVFallergySeverity.html)</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -93,6 +94,36 @@
   </si>
   <si>
     <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>MILD</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>MODERATE</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>SEVERE</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://va.gov/terminology/vistaDefinedElements/120.85-14.5</t>
   </si>
 </sst>
 </file>
@@ -270,24 +301,22 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s" s="2">
         <v>12</v>
       </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -347,6 +376,68 @@
       </c>
       <c r="B15" t="s" s="2">
         <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -316,66 +319,68 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -394,50 +399,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from 120.85-14.5" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from AllergyIntoleran" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
   <si>
     <t>Property</t>
   </si>
@@ -30,21 +31,18 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>VSVFallergySeverity</t>
+    <t>VF_allergySeverity</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>VF_allergySeverity</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -60,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,6 +125,18 @@
   </si>
   <si>
     <t>http://va.gov/terminology/vistaDefinedElements/120.85-14.5</t>
+  </si>
+  <si>
+    <t>mild</t>
+  </si>
+  <si>
+    <t>moderate</t>
+  </si>
+  <si>
+    <t>severe</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/reaction-event-severity</t>
   </si>
 </sst>
 </file>
@@ -304,83 +314,83 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>12</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -399,50 +409,106 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>36</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="B6" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from 120.85-14.5" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from AllergyIntoleran" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from AllergyIntoleran" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from 120.85-14.5" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Navigate to [ConceptMap VF_allergySeverity](ConceptMap-CMVFallergySeverity.html)</t>
+    <t>Navigate to [ConceptMap VF_allergySeverity](ConceptMap-CMVFallergySeverity.html)
+&gt; Note that the FHIR binding is to the codes in the fhir system. The codes from the VistADefinedElements system are map source codes: they may be included in addition to the fhir codes, but they don't address the binding requirement.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,6 +101,24 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>mild</t>
+  </si>
+  <si>
+    <t>moderate</t>
+  </si>
+  <si>
+    <t>severe</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/reaction-event-severity</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -118,25 +137,7 @@
     <t>SEVERE</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
     <t>http://va.gov/terminology/vistaDefinedElements/120.85-14.5</t>
-  </si>
-  <si>
-    <t>mild</t>
-  </si>
-  <si>
-    <t>moderate</t>
-  </si>
-  <si>
-    <t>severe</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/reaction-event-severity</t>
   </si>
 </sst>
 </file>
@@ -419,40 +420,34 @@
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>29</v>
-      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -479,33 +474,39 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>40</v>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,10 +82,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Navigate to [ConceptMap VF_allergySeverity](ConceptMap-CMVFallergySeverity.html)
-&gt; Note that the FHIR binding is to the codes in the fhir system. The codes from the VistADefinedElements system are map source codes: they may be included in addition to the fhir codes, but they don't address the binding requirement.</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -137,7 +133,7 @@
     <t>SEVERE</t>
   </si>
   <si>
-    <t>http://va.gov/terminology/vistaDefinedElements/120.85-14.5</t>
+    <t>http://va.gov/terminology/vistaDefinedTerms/120.85-14.5</t>
   </si>
 </sst>
 </file>
@@ -370,28 +366,26 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -410,7 +404,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -418,36 +412,36 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -466,7 +460,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -474,42 +468,42 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>ValueSet for terminology map VF_allergySeverity</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -366,26 +369,28 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -404,7 +409,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -412,36 +417,36 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -460,7 +465,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -468,42 +473,42 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet for terminology map VF_allergySeverity</t>
+    <t>ValueSet for Terminology Maps VF_allergySeverity</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -8,13 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from AllergyIntoleran" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from 120.85-14.5" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -52,13 +51,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet for Terminology Maps VF_allergySeverity</t>
+    <t>FHIR Target ValueSet for Terminology Maps VF_allergySeverity</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -116,27 +115,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/reaction-event-severity</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>MILD</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>MODERATE</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>SEVERE</t>
-  </si>
-  <si>
-    <t>http://va.gov/terminology/vistaDefinedTerms/120.85-14.5</t>
   </si>
 </sst>
 </file>
@@ -452,66 +430,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from AllergyIntoleran" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFallergySeverity.xlsx
+++ b/docs/ValueSet-VSVFallergySeverity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
